--- a/results_(stress_test)_PCCxSigmoid-PLV-/cnn_evaluation(stress_test)_k-20_p-30_nm_basis-False_nm_modifier-False.xlsx
+++ b/results_(stress_test)_PCCxSigmoid-PLV-/cnn_evaluation(stress_test)_k-20_p-30_nm_basis-False_nm_modifier-False.xlsx
@@ -12,6 +12,8 @@
     <sheet name="summary_t" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="nrr_32" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="nrr_16" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="nrr_8" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="nrr_4" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1078,7 +1080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1217,6 +1219,82 @@
         <v>3.51207039195088</v>
       </c>
       <c r="E7" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>76.43559777045361</v>
+      </c>
+      <c r="B8" t="n">
+        <v>75.9782323787682</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.5876927329713645</v>
+      </c>
+      <c r="D8" t="n">
+        <v>76.43559777045361</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8.495777964228171</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8.766706205234804</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1977004991160216</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8.49577796422817</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>56.69291833551039</v>
+      </c>
+      <c r="B10" t="n">
+        <v>54.33778589492066</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.027108851776769</v>
+      </c>
+      <c r="D10" t="n">
+        <v>56.69291833551039</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>8.52708556808242</v>
+      </c>
+      <c r="B11" t="n">
+        <v>9.444855736926618</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.1930738197626725</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8.527085568082418</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>Std</t>
         </is>
@@ -1233,7 +1311,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1354,6 +1432,58 @@
       </c>
       <c r="H4" t="n">
         <v>0.1251480355529196</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>76.43559777045361</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8.495777964228171</v>
+      </c>
+      <c r="C5" t="n">
+        <v>75.9782323787682</v>
+      </c>
+      <c r="D5" t="n">
+        <v>8.766706205234804</v>
+      </c>
+      <c r="E5" t="n">
+        <v>76.43559777045361</v>
+      </c>
+      <c r="F5" t="n">
+        <v>8.49577796422817</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5876927329713645</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.1977004991160216</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>56.69291833551039</v>
+      </c>
+      <c r="B6" t="n">
+        <v>8.52708556808242</v>
+      </c>
+      <c r="C6" t="n">
+        <v>54.33778589492066</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9.444855736926618</v>
+      </c>
+      <c r="E6" t="n">
+        <v>56.69291833551039</v>
+      </c>
+      <c r="F6" t="n">
+        <v>8.527085568082418</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.027108851776769</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.1930738197626725</v>
       </c>
     </row>
   </sheetData>
@@ -2657,4 +2787,1302 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1_score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>78.21304682566458</v>
+      </c>
+      <c r="C2" t="n">
+        <v>77.6385862242095</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.5386199260130524</v>
+      </c>
+      <c r="E2" t="n">
+        <v>78.21304682566458</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>82.49223609200772</v>
+      </c>
+      <c r="C3" t="n">
+        <v>82.32749572296001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.4315269549765314</v>
+      </c>
+      <c r="E3" t="n">
+        <v>82.49223609200772</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>81.72077613128141</v>
+      </c>
+      <c r="C4" t="n">
+        <v>81.33535404945864</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.451693798104922</v>
+      </c>
+      <c r="E4" t="n">
+        <v>81.72077613128141</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>69.1390928987275</v>
+      </c>
+      <c r="C5" t="n">
+        <v>68.35197527506364</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.6870428326229254</v>
+      </c>
+      <c r="E5" t="n">
+        <v>69.1390928987275</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>70.93296654815353</v>
+      </c>
+      <c r="C6" t="n">
+        <v>71.00716365402731</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.6936874687671661</v>
+      </c>
+      <c r="E6" t="n">
+        <v>70.93296654815353</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>63.33688007681727</v>
+      </c>
+      <c r="C7" t="n">
+        <v>63.10482575528742</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.8624639113744099</v>
+      </c>
+      <c r="E7" t="n">
+        <v>63.33688007681727</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>80.07750932101489</v>
+      </c>
+      <c r="C8" t="n">
+        <v>79.90928082516344</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4592081332967307</v>
+      </c>
+      <c r="E8" t="n">
+        <v>80.07750932101489</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>86.77038728708726</v>
+      </c>
+      <c r="C9" t="n">
+        <v>86.77648071735959</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.3285393545404077</v>
+      </c>
+      <c r="E9" t="n">
+        <v>86.77038728708726</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>85.8505696416059</v>
+      </c>
+      <c r="C10" t="n">
+        <v>86.00408208082074</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.3619837363560995</v>
+      </c>
+      <c r="E10" t="n">
+        <v>85.8505696416059</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>82.78877844964057</v>
+      </c>
+      <c r="C11" t="n">
+        <v>82.30847880890937</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.43096582206587</v>
+      </c>
+      <c r="E11" t="n">
+        <v>82.78877844964056</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>78.06226697462782</v>
+      </c>
+      <c r="C12" t="n">
+        <v>78.21350883326134</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5785457262148459</v>
+      </c>
+      <c r="E12" t="n">
+        <v>78.06226697462782</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>80.14204275123487</v>
+      </c>
+      <c r="C13" t="n">
+        <v>79.97527985927539</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.5635447690884272</v>
+      </c>
+      <c r="E13" t="n">
+        <v>80.14204275123487</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>66.10593517244959</v>
+      </c>
+      <c r="C14" t="n">
+        <v>64.85662783863769</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.7879786387085914</v>
+      </c>
+      <c r="E14" t="n">
+        <v>66.10593517244959</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>67.28812532980389</v>
+      </c>
+      <c r="C15" t="n">
+        <v>66.73142956459971</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.7504031655689081</v>
+      </c>
+      <c r="E15" t="n">
+        <v>67.28812532980389</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>62.94855491829514</v>
+      </c>
+      <c r="C16" t="n">
+        <v>62.36521867262523</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.9197414418061574</v>
+      </c>
+      <c r="E16" t="n">
+        <v>62.94855491829514</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>81.5479372658933</v>
+      </c>
+      <c r="C17" t="n">
+        <v>81.36585045393196</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.4734066039013366</v>
+      </c>
+      <c r="E17" t="n">
+        <v>81.5479372658933</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>77.39729582435834</v>
+      </c>
+      <c r="C18" t="n">
+        <v>76.12977092071941</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.6582373173596958</v>
+      </c>
+      <c r="E18" t="n">
+        <v>77.39729582435834</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>86.99564875128678</v>
+      </c>
+      <c r="C19" t="n">
+        <v>87.00177206455596</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.3573584439232945</v>
+      </c>
+      <c r="E19" t="n">
+        <v>86.99564875128678</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>72.02198980960043</v>
+      </c>
+      <c r="C20" t="n">
+        <v>71.48095383588921</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.6771978035569191</v>
+      </c>
+      <c r="E20" t="n">
+        <v>72.02198980960043</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>62.00996548413049</v>
+      </c>
+      <c r="C21" t="n">
+        <v>60.39043119908005</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.9820092582609504</v>
+      </c>
+      <c r="E21" t="n">
+        <v>62.00996548413049</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>75.0153548041073</v>
+      </c>
+      <c r="C22" t="n">
+        <v>73.87084812678128</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.6784440857668718</v>
+      </c>
+      <c r="E22" t="n">
+        <v>75.0153548041073</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>69.14514831443179</v>
+      </c>
+      <c r="C23" t="n">
+        <v>67.96177386963846</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.7190287125607331</v>
+      </c>
+      <c r="E23" t="n">
+        <v>69.14514831443179</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>77.42143098123685</v>
+      </c>
+      <c r="C24" t="n">
+        <v>76.88173168891217</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.5780703061570723</v>
+      </c>
+      <c r="E24" t="n">
+        <v>77.42143098123685</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>71.79274907222381</v>
+      </c>
+      <c r="C25" t="n">
+        <v>72.04287782956777</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.6127463546892007</v>
+      </c>
+      <c r="E25" t="n">
+        <v>71.79274907222381</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>80.30588499900519</v>
+      </c>
+      <c r="C26" t="n">
+        <v>79.74590229466085</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.4933740068847935</v>
+      </c>
+      <c r="E26" t="n">
+        <v>80.30588499900519</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>60.08667895050995</v>
+      </c>
+      <c r="C27" t="n">
+        <v>59.06847922800006</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.9991003615160784</v>
+      </c>
+      <c r="E27" t="n">
+        <v>60.08667895050995</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>76.76640801391015</v>
+      </c>
+      <c r="C28" t="n">
+        <v>76.36614277413153</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.6457343824207783</v>
+      </c>
+      <c r="E28" t="n">
+        <v>76.76640801391015</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>86.22886011124663</v>
+      </c>
+      <c r="C29" t="n">
+        <v>86.08958183683313</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.3705604353298744</v>
+      </c>
+      <c r="E29" t="n">
+        <v>86.22886011124663</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>89.24670628638657</v>
+      </c>
+      <c r="C30" t="n">
+        <v>89.19383716728905</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.3043285809766531</v>
+      </c>
+      <c r="E30" t="n">
+        <v>89.24670628638656</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>91.21670602686875</v>
+      </c>
+      <c r="C31" t="n">
+        <v>90.85123019139598</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.2352396563316385</v>
+      </c>
+      <c r="E31" t="n">
+        <v>91.21670602686875</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>76.43559777045361</v>
+      </c>
+      <c r="C32" t="n">
+        <v>75.9782323787682</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.5876927329713645</v>
+      </c>
+      <c r="E32" t="n">
+        <v>76.43559777045361</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>8.495777964228171</v>
+      </c>
+      <c r="C33" t="n">
+        <v>8.766706205234804</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1977004991160216</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8.49577796422817</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Identifier</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>f1_score</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>recall</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>sub6ex1</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>53.08817550324829</v>
+      </c>
+      <c r="C2" t="n">
+        <v>49.23907186010537</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.116821657617887</v>
+      </c>
+      <c r="E2" t="n">
+        <v>53.08817550324831</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>sub6ex2</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>56.57696000830457</v>
+      </c>
+      <c r="C3" t="n">
+        <v>53.6310821780591</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.004528341690699</v>
+      </c>
+      <c r="E3" t="n">
+        <v>56.57696000830457</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sub6ex3</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>62.83557816244085</v>
+      </c>
+      <c r="C4" t="n">
+        <v>61.96471534493499</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.8976399083932242</v>
+      </c>
+      <c r="E4" t="n">
+        <v>62.83557816244085</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sub7ex1</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>50.22751061860397</v>
+      </c>
+      <c r="C5" t="n">
+        <v>47.9386408540587</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.06080305899183</v>
+      </c>
+      <c r="E5" t="n">
+        <v>50.22751061860397</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sub7ex2</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>51.14404103841728</v>
+      </c>
+      <c r="C6" t="n">
+        <v>48.79259597452952</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.026770191888014</v>
+      </c>
+      <c r="E6" t="n">
+        <v>51.14404103841728</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sub7ex3</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>48.48778968676199</v>
+      </c>
+      <c r="C7" t="n">
+        <v>46.01228830512859</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.114142127831777</v>
+      </c>
+      <c r="E7" t="n">
+        <v>48.48778968676199</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sub8ex1</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>67.64158859505706</v>
+      </c>
+      <c r="C8" t="n">
+        <v>66.97362456957353</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.7403451437751453</v>
+      </c>
+      <c r="E8" t="n">
+        <v>67.64158859505704</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sub8ex2</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>59.92750802342581</v>
+      </c>
+      <c r="C9" t="n">
+        <v>55.31174725851398</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.076683080444733</v>
+      </c>
+      <c r="E9" t="n">
+        <v>59.92750802342581</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sub8ex3</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>63.6984749003019</v>
+      </c>
+      <c r="C10" t="n">
+        <v>61.32284297030708</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.8639314383268356</v>
+      </c>
+      <c r="E10" t="n">
+        <v>63.6984749003019</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sub9ex1</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>52.76334570368256</v>
+      </c>
+      <c r="C11" t="n">
+        <v>51.28449013456174</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.15306477646033</v>
+      </c>
+      <c r="E11" t="n">
+        <v>52.76334570368256</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>sub9ex2</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>48.66408878969541</v>
+      </c>
+      <c r="C12" t="n">
+        <v>44.4047369735995</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.358957561850548</v>
+      </c>
+      <c r="E12" t="n">
+        <v>48.66408878969541</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>sub9ex3</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>50.71384700559693</v>
+      </c>
+      <c r="C13" t="n">
+        <v>47.08678296192736</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.204393244783084</v>
+      </c>
+      <c r="E13" t="n">
+        <v>50.71384700559694</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>sub10ex1</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>47.4339743423386</v>
+      </c>
+      <c r="C14" t="n">
+        <v>44.13080083591387</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.160145123799642</v>
+      </c>
+      <c r="E14" t="n">
+        <v>47.4339743423386</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>sub10ex2</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>48.93857213297693</v>
+      </c>
+      <c r="C15" t="n">
+        <v>45.59259655519712</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.147330910960833</v>
+      </c>
+      <c r="E15" t="n">
+        <v>48.93857213297693</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sub10ex3</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>49.52214119499304</v>
+      </c>
+      <c r="C16" t="n">
+        <v>46.65582460179301</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.159040263295174</v>
+      </c>
+      <c r="E16" t="n">
+        <v>49.52214119499304</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>sub11ex1</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>56.26969091428126</v>
+      </c>
+      <c r="C17" t="n">
+        <v>52.72596901352934</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.14130559793363</v>
+      </c>
+      <c r="E17" t="n">
+        <v>56.26969091428126</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>sub11ex2</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>61.42812654088704</v>
+      </c>
+      <c r="C18" t="n">
+        <v>59.2865188993163</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.8843126922845841</v>
+      </c>
+      <c r="E18" t="n">
+        <v>61.42812654088702</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>sub11ex3</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>63.54319674045623</v>
+      </c>
+      <c r="C19" t="n">
+        <v>62.48469314678397</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.8426320806145668</v>
+      </c>
+      <c r="E19" t="n">
+        <v>63.54319674045623</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>sub12ex1</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>56.74132129170668</v>
+      </c>
+      <c r="C20" t="n">
+        <v>55.37201771368969</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.051320252319177</v>
+      </c>
+      <c r="E20" t="n">
+        <v>56.74132129170668</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>sub12ex2</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>51.85511985397797</v>
+      </c>
+      <c r="C21" t="n">
+        <v>48.71451563938346</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.294225414594014</v>
+      </c>
+      <c r="E21" t="n">
+        <v>51.85511985397797</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>sub12ex3</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>60.3075286118392</v>
+      </c>
+      <c r="C22" t="n">
+        <v>58.88547589322719</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.9450259298086167</v>
+      </c>
+      <c r="E22" t="n">
+        <v>60.3075286118392</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>sub13ex1</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>53.08488827758025</v>
+      </c>
+      <c r="C23" t="n">
+        <v>50.36994417188144</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1.05799170533816</v>
+      </c>
+      <c r="E23" t="n">
+        <v>53.08488827758025</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>sub13ex2</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>49.26253687315634</v>
+      </c>
+      <c r="C24" t="n">
+        <v>46.66631729025603</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.135303491353989</v>
+      </c>
+      <c r="E24" t="n">
+        <v>49.26253687315634</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>sub13ex3</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>50.52370695248229</v>
+      </c>
+      <c r="C25" t="n">
+        <v>49.33428991217277</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.066205113132795</v>
+      </c>
+      <c r="E25" t="n">
+        <v>50.52370695248229</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>sub14ex1</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>62.08989697142708</v>
+      </c>
+      <c r="C26" t="n">
+        <v>60.29952054430983</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.9055201448500156</v>
+      </c>
+      <c r="E26" t="n">
+        <v>62.08989697142708</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>sub14ex2</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>49.01945518559849</v>
+      </c>
+      <c r="C27" t="n">
+        <v>46.27295626247951</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1.188317606846491</v>
+      </c>
+      <c r="E27" t="n">
+        <v>49.01945518559849</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>sub14ex3</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>49.86081194474001</v>
+      </c>
+      <c r="C28" t="n">
+        <v>44.79345514386507</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1.25391016403834</v>
+      </c>
+      <c r="E28" t="n">
+        <v>49.86081194474001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>sub15ex1</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>70.87076877827663</v>
+      </c>
+      <c r="C29" t="n">
+        <v>70.51669595643526</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.7232207601269086</v>
+      </c>
+      <c r="E29" t="n">
+        <v>70.87076877827663</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>sub15ex2</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>69.55985778423688</v>
+      </c>
+      <c r="C30" t="n">
+        <v>69.59687136329124</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.8307962581515312</v>
+      </c>
+      <c r="E30" t="n">
+        <v>69.55985778423688</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>sub15ex3</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>84.7070476388204</v>
+      </c>
+      <c r="C31" t="n">
+        <v>84.47249451879524</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.4085815118004878</v>
+      </c>
+      <c r="E31" t="n">
+        <v>84.7070476388204</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>56.69291833551039</v>
+      </c>
+      <c r="C32" t="n">
+        <v>54.33778589492066</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1.027108851776769</v>
+      </c>
+      <c r="E32" t="n">
+        <v>56.69291833551039</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Std</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>8.52708556808242</v>
+      </c>
+      <c r="C33" t="n">
+        <v>9.444855736926618</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1930738197626725</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8.527085568082418</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>